--- a/sheets/민요/검수/쑥대머리 (중모리).xlsx
+++ b/sheets/민요/검수/쑥대머리 (중모리).xlsx
@@ -413,7 +413,7 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">― 연음 · △ 쉼 · 점 · ○ 동그라미 · ⁚ 두 점 · ‹ 정간 경계 표시 · ／ 사선 (· ○ ⁚ ‹ ／ 는 화면 표시 전용)</t>
+          <t xml:space="preserve">– 연음 · △ 쉼 · 점 · ○ 동그라미 · ⁚ 두 점 · ‹ 정간 경계 표시 · ／ 사선 (· ○ ⁚ ‹ ／ 는 화면 표시 전용)</t>
         </is>
       </c>
     </row>
@@ -1042,12 +1042,12 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―|南</t>
+          <t xml:space="preserve">–|南</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 南</t>
         </is>
       </c>
@@ -1191,12 +1191,12 @@
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―|△</t>
+          <t xml:space="preserve">–|△</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 △</t>
         </is>
       </c>
@@ -1533,12 +1533,12 @@
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -1866,12 +1866,12 @@
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―|△</t>
+          <t xml:space="preserve">–|△</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 △</t>
         </is>
       </c>
@@ -2099,12 +2099,12 @@
       </c>
       <c r="G43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">―|潢</t>
+          <t xml:space="preserve">–|潢</t>
         </is>
       </c>
       <c r="H43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 潢</t>
         </is>
       </c>
@@ -2300,12 +2300,12 @@
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I48" s="2"/>
@@ -2453,7 +2453,7 @@
       </c>
       <c r="F4" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 南</t>
         </is>
       </c>
@@ -2484,7 +2484,7 @@
       <c r="C5" s="13"/>
       <c r="D5" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="E5" s="10" t="inlineStr">
@@ -2576,7 +2576,7 @@
       <c r="A8" s="0"/>
       <c r="B8" s="18" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 潢</t>
         </is>
       </c>
@@ -2590,7 +2590,7 @@
       <c r="E8" s="10"/>
       <c r="F8" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 △</t>
         </is>
       </c>
@@ -2750,7 +2750,7 @@
       <c r="A13" s="0"/>
       <c r="B13" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="C13" s="9"/>
@@ -2787,7 +2787,7 @@
       <c r="C14" s="10"/>
       <c r="D14" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 △</t>
         </is>
       </c>

--- a/sheets/민요/검수/쑥대머리 (중모리).xlsx
+++ b/sheets/민요/검수/쑥대머리 (중모리).xlsx
@@ -11,27 +11,43 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="4">
+  <fonts count="7">
     <font>
       <sz val="11"/>
-      <name val="맑은 고딕"/>
+      <name val="궁서체"/>
       <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
-      <name val="맑은 고딕"/>
+      <name val="궁서체"/>
       <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="14"/>
-      <name val="맑은 고딕"/>
+      <name val="궁서체"/>
       <family val="2"/>
     </font>
     <font>
       <sz val="22"/>
-      <name val="맑은 고딕"/>
+      <name val="궁서체"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="24"/>
+      <name val="궁서체"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="24"/>
+      <name val="궁서체"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <name val="궁서체"/>
       <family val="2"/>
     </font>
   </fonts>
@@ -134,7 +150,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -157,7 +173,6 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <!-- 8~16: 박 묶음 가사 칸 = (일반 8~10 · 비고 11~13 · 팔레트 외 14~16) × (첫 · 가운데 · 마지막) -->
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -185,7 +200,6 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <!-- 17~19: 악보 율명 칸 22pt (가사 11pt 의 두 배) = 일반 · 비고 · 팔레트 외 -->
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -193,6 +207,33 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -2371,59 +2412,59 @@
     </row>
     <row r="2" ht="60" customHeight="1">
       <c r="A2" s="0"/>
-      <c r="B2" s="7" t="inlineStr">
+      <c r="B2" s="20" t="inlineStr">
         <is>
           <t xml:space="preserve">쑥대머리</t>
         </is>
       </c>
-      <c r="C2" s="7"/>
-      <c r="D2" s="7"/>
-      <c r="E2" s="7"/>
-      <c r="F2" s="7"/>
-      <c r="G2" s="7"/>
-      <c r="H2" s="7"/>
-      <c r="I2" s="7"/>
+      <c r="C2" s="20"/>
+      <c r="D2" s="20"/>
+      <c r="E2" s="20"/>
+      <c r="F2" s="20"/>
+      <c r="G2" s="20"/>
+      <c r="H2" s="20"/>
+      <c r="I2" s="20"/>
     </row>
     <row r="3" ht="56" customHeight="1">
       <c r="A3" s="0"/>
-      <c r="B3" s="17" t="inlineStr">
+      <c r="B3" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="C3" s="8" t="inlineStr">
+      <c r="C3" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">막</t>
         </is>
       </c>
-      <c r="D3" s="17" t="inlineStr">
+      <c r="D3" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南
 潢</t>
         </is>
       </c>
-      <c r="E3" s="8" t="inlineStr">
+      <c r="E3" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">번</t>
         </is>
       </c>
-      <c r="F3" s="17" t="inlineStr">
+      <c r="F3" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="G3" s="8" t="inlineStr">
+      <c r="G3" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">계</t>
         </is>
       </c>
-      <c r="H3" s="17" t="inlineStr">
+      <c r="H3" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
 潢潢</t>
         </is>
       </c>
-      <c r="I3" s="8" t="inlineStr">
+      <c r="I3" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">예</t>
         </is>
@@ -2431,43 +2472,43 @@
     </row>
     <row r="4" ht="56" customHeight="1">
       <c r="A4" s="0"/>
-      <c r="B4" s="17" t="inlineStr">
+      <c r="B4" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="C4" s="9" t="inlineStr">
+      <c r="C4" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">왕</t>
         </is>
       </c>
-      <c r="D4" s="17" t="inlineStr">
+      <c r="D4" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="E4" s="9" t="inlineStr">
+      <c r="E4" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">듯</t>
         </is>
       </c>
-      <c r="F4" s="17" t="inlineStr">
+      <c r="F4" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 南</t>
         </is>
       </c>
-      <c r="G4" s="9" t="inlineStr">
+      <c r="G4" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">궁</t>
         </is>
       </c>
-      <c r="H4" s="17" t="inlineStr">
+      <c r="H4" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢潢</t>
         </is>
       </c>
-      <c r="I4" s="9" t="inlineStr">
+      <c r="I4" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">의</t>
         </is>
@@ -2475,39 +2516,39 @@
     </row>
     <row r="5" ht="56" customHeight="1">
       <c r="A5" s="0"/>
-      <c r="B5" s="18" t="inlineStr">
+      <c r="B5" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">淋
 潢</t>
         </is>
       </c>
-      <c r="C5" s="13"/>
-      <c r="D5" s="17" t="inlineStr">
+      <c r="C5" s="25"/>
+      <c r="D5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="E5" s="10" t="inlineStr">
+      <c r="E5" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">이</t>
         </is>
       </c>
-      <c r="F5" s="17" t="inlineStr">
+      <c r="F5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南南</t>
         </is>
       </c>
-      <c r="G5" s="10" t="inlineStr">
+      <c r="G5" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">항아</t>
         </is>
       </c>
-      <c r="H5" s="17" t="inlineStr">
+      <c r="H5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢潢</t>
         </is>
       </c>
-      <c r="I5" s="10" t="inlineStr">
+      <c r="I5" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">신혼</t>
         </is>
@@ -2515,295 +2556,295 @@
     </row>
     <row r="6" ht="56" customHeight="1">
       <c r="A6" s="0"/>
-      <c r="B6" s="18" t="inlineStr">
+      <c r="B6" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 △</t>
         </is>
       </c>
-      <c r="C6" s="11"/>
-      <c r="D6" s="17" t="inlineStr">
+      <c r="C6" s="27"/>
+      <c r="D6" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">△</t>
         </is>
       </c>
-      <c r="E6" s="8"/>
-      <c r="F6" s="17" t="inlineStr">
+      <c r="E6" s="22"/>
+      <c r="F6" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="G6" s="8"/>
-      <c r="H6" s="17" t="inlineStr">
+      <c r="G6" s="22"/>
+      <c r="H6" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢潢</t>
         </is>
       </c>
-      <c r="I6" s="8"/>
+      <c r="I6" s="22"/>
     </row>
     <row r="7" ht="56" customHeight="1">
       <c r="A7" s="0"/>
-      <c r="B7" s="17" t="inlineStr">
+      <c r="B7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="C7" s="9" t="inlineStr">
+      <c r="C7" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">막</t>
         </is>
       </c>
-      <c r="D7" s="17" t="inlineStr">
+      <c r="D7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="E7" s="9"/>
-      <c r="F7" s="17" t="inlineStr">
+      <c r="E7" s="23"/>
+      <c r="F7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="G7" s="9"/>
-      <c r="H7" s="17" t="inlineStr">
+      <c r="G7" s="23"/>
+      <c r="H7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="I7" s="9"/>
+      <c r="I7" s="23"/>
     </row>
     <row r="8" ht="56" customHeight="1">
       <c r="A8" s="0"/>
-      <c r="B8" s="18" t="inlineStr">
+      <c r="B8" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 潢</t>
         </is>
       </c>
-      <c r="C8" s="13"/>
-      <c r="D8" s="17" t="inlineStr">
+      <c r="C8" s="25"/>
+      <c r="D8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 姑</t>
         </is>
       </c>
-      <c r="E8" s="10"/>
-      <c r="F8" s="17" t="inlineStr">
+      <c r="E8" s="26"/>
+      <c r="F8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 △</t>
         </is>
       </c>
-      <c r="G8" s="10"/>
-      <c r="H8" s="17" t="inlineStr">
+      <c r="G8" s="26"/>
+      <c r="H8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="I8" s="10"/>
+      <c r="I8" s="26"/>
     </row>
     <row r="9" ht="56" customHeight="1">
       <c r="A9" s="0"/>
-      <c r="B9" s="18" t="inlineStr">
+      <c r="B9" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">潢潢
 姑</t>
         </is>
       </c>
-      <c r="C9" s="11" t="inlineStr">
+      <c r="C9" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">막혀</t>
         </is>
       </c>
-      <c r="D9" s="17" t="inlineStr">
+      <c r="D9" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 南</t>
         </is>
       </c>
-      <c r="E9" s="8" t="inlineStr">
+      <c r="E9" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">비</t>
         </is>
       </c>
-      <c r="F9" s="18" t="inlineStr">
+      <c r="F9" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">潢潢
 姑</t>
         </is>
       </c>
-      <c r="G9" s="11" t="inlineStr">
+      <c r="G9" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">추</t>
         </is>
       </c>
-      <c r="H9" s="17" t="inlineStr">
+      <c r="H9" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢汰
 潢汰</t>
         </is>
       </c>
-      <c r="I9" s="8"/>
+      <c r="I9" s="22"/>
     </row>
     <row r="10" ht="56" customHeight="1">
       <c r="A10" s="0"/>
-      <c r="B10" s="17" t="inlineStr">
+      <c r="B10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="C10" s="9" t="inlineStr">
+      <c r="C10" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">막혀</t>
         </is>
       </c>
-      <c r="D10" s="17" t="inlineStr">
+      <c r="D10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="E10" s="9" t="inlineStr">
+      <c r="E10" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">치</t>
         </is>
       </c>
-      <c r="F10" s="17" t="inlineStr">
+      <c r="F10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="G10" s="9"/>
-      <c r="H10" s="17" t="inlineStr">
+      <c r="G10" s="23"/>
+      <c r="H10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢汰</t>
         </is>
       </c>
-      <c r="I10" s="9"/>
+      <c r="I10" s="23"/>
     </row>
     <row r="11" ht="56" customHeight="1">
       <c r="A11" s="0"/>
-      <c r="B11" s="17" t="inlineStr">
+      <c r="B11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="C11" s="10" t="inlineStr">
+      <c r="C11" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">니</t>
         </is>
       </c>
-      <c r="D11" s="18" t="inlineStr">
+      <c r="D11" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="E11" s="13"/>
-      <c r="F11" s="17" t="inlineStr">
+      <c r="E11" s="25"/>
+      <c r="F11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="G11" s="10"/>
-      <c r="H11" s="18" t="inlineStr">
+      <c r="G11" s="26"/>
+      <c r="H11" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">／</t>
         </is>
       </c>
-      <c r="I11" s="13"/>
+      <c r="I11" s="25"/>
     </row>
     <row r="12" ht="56" customHeight="1">
       <c r="A12" s="0"/>
-      <c r="B12" s="17" t="inlineStr">
+      <c r="B12" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="C12" s="8" t="inlineStr">
+      <c r="C12" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">니</t>
         </is>
       </c>
-      <c r="D12" s="17" t="inlineStr">
+      <c r="D12" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="E12" s="8"/>
-      <c r="F12" s="17" t="inlineStr">
+      <c r="E12" s="22"/>
+      <c r="F12" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="G12" s="8" t="inlineStr">
+      <c r="G12" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">갈</t>
         </is>
       </c>
-      <c r="H12" s="18" t="inlineStr">
+      <c r="H12" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">潢潢</t>
         </is>
       </c>
-      <c r="I12" s="11"/>
+      <c r="I12" s="27"/>
     </row>
     <row r="13" ht="56" customHeight="1">
       <c r="A13" s="0"/>
-      <c r="B13" s="17" t="inlineStr">
+      <c r="B13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="C13" s="9"/>
-      <c r="D13" s="17" t="inlineStr">
+      <c r="C13" s="23"/>
+      <c r="D13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="E13" s="9"/>
-      <c r="F13" s="17" t="inlineStr">
+      <c r="E13" s="23"/>
+      <c r="F13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="G13" s="9" t="inlineStr">
+      <c r="G13" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">이</t>
         </is>
       </c>
-      <c r="H13" s="18" t="inlineStr">
+      <c r="H13" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="I13" s="12"/>
+      <c r="I13" s="28"/>
     </row>
     <row r="14" ht="56" customHeight="1">
       <c r="A14" s="0"/>
-      <c r="B14" s="17" t="inlineStr">
+      <c r="B14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="C14" s="10"/>
-      <c r="D14" s="17" t="inlineStr">
+      <c r="C14" s="26"/>
+      <c r="D14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 △</t>
         </is>
       </c>
-      <c r="E14" s="10"/>
-      <c r="F14" s="17" t="inlineStr">
+      <c r="E14" s="26"/>
+      <c r="F14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="G14" s="10"/>
-      <c r="H14" s="18" t="inlineStr">
+      <c r="G14" s="26"/>
+      <c r="H14" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="I14" s="13"/>
+      <c r="I14" s="25"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/sheets/민요/검수/쑥대머리 (중모리).xlsx
+++ b/sheets/민요/검수/쑥대머리 (중모리).xlsx
@@ -2397,20 +2397,20 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
-    <col min="2" max="2" width="9" customWidth="1"/>
+    <col min="2" max="2" width="12" customWidth="1"/>
     <col min="3" max="3" width="6" customWidth="1"/>
-    <col min="4" max="4" width="9" customWidth="1"/>
+    <col min="4" max="4" width="12" customWidth="1"/>
     <col min="5" max="5" width="6" customWidth="1"/>
-    <col min="6" max="6" width="9" customWidth="1"/>
+    <col min="6" max="6" width="12" customWidth="1"/>
     <col min="7" max="7" width="6" customWidth="1"/>
-    <col min="8" max="8" width="9" customWidth="1"/>
+    <col min="8" max="8" width="12" customWidth="1"/>
     <col min="9" max="9" width="6" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="0"/>
     </row>
-    <row r="2" ht="60" customHeight="1">
+    <row r="2" ht="55.19" customHeight="1">
       <c r="A2" s="0"/>
       <c r="B2" s="20" t="inlineStr">
         <is>
@@ -2425,7 +2425,7 @@
       <c r="H2" s="20"/>
       <c r="I2" s="20"/>
     </row>
-    <row r="3" ht="56" customHeight="1">
+    <row r="3" ht="55.19" customHeight="1">
       <c r="A3" s="0"/>
       <c r="B3" s="21" t="inlineStr">
         <is>
@@ -2470,7 +2470,7 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="56" customHeight="1">
+    <row r="4" ht="55.19" customHeight="1">
       <c r="A4" s="0"/>
       <c r="B4" s="21" t="inlineStr">
         <is>
@@ -2484,7 +2484,7 @@
       </c>
       <c r="D4" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="E4" s="23" t="inlineStr">
@@ -2514,7 +2514,7 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="56" customHeight="1">
+    <row r="5" ht="55.19" customHeight="1">
       <c r="A5" s="0"/>
       <c r="B5" s="24" t="inlineStr">
         <is>
@@ -2554,7 +2554,7 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="56" customHeight="1">
+    <row r="6" ht="55.19" customHeight="1">
       <c r="A6" s="0"/>
       <c r="B6" s="24" t="inlineStr">
         <is>
@@ -2571,7 +2571,7 @@
       <c r="E6" s="22"/>
       <c r="F6" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="G6" s="22"/>
@@ -2582,7 +2582,7 @@
       </c>
       <c r="I6" s="22"/>
     </row>
-    <row r="7" ht="56" customHeight="1">
+    <row r="7" ht="55.19" customHeight="1">
       <c r="A7" s="0"/>
       <c r="B7" s="21" t="inlineStr">
         <is>
@@ -2602,18 +2602,18 @@
       <c r="E7" s="23"/>
       <c r="F7" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="G7" s="23"/>
       <c r="H7" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I7" s="23"/>
     </row>
-    <row r="8" ht="56" customHeight="1">
+    <row r="8" ht="55.19" customHeight="1">
       <c r="A8" s="0"/>
       <c r="B8" s="24" t="inlineStr">
         <is>
@@ -2643,7 +2643,7 @@
       </c>
       <c r="I8" s="26"/>
     </row>
-    <row r="9" ht="56" customHeight="1">
+    <row r="9" ht="55.19" customHeight="1">
       <c r="A9" s="0"/>
       <c r="B9" s="24" t="inlineStr">
         <is>
@@ -2686,7 +2686,7 @@
       </c>
       <c r="I9" s="22"/>
     </row>
-    <row r="10" ht="56" customHeight="1">
+    <row r="10" ht="55.19" customHeight="1">
       <c r="A10" s="0"/>
       <c r="B10" s="21" t="inlineStr">
         <is>
@@ -2700,7 +2700,7 @@
       </c>
       <c r="D10" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="E10" s="23" t="inlineStr">
@@ -2721,7 +2721,7 @@
       </c>
       <c r="I10" s="23"/>
     </row>
-    <row r="11" ht="56" customHeight="1">
+    <row r="11" ht="55.19" customHeight="1">
       <c r="A11" s="0"/>
       <c r="B11" s="21" t="inlineStr">
         <is>
@@ -2752,7 +2752,7 @@
       </c>
       <c r="I11" s="25"/>
     </row>
-    <row r="12" ht="56" customHeight="1">
+    <row r="12" ht="55.19" customHeight="1">
       <c r="A12" s="0"/>
       <c r="B12" s="21" t="inlineStr">
         <is>
@@ -2787,7 +2787,7 @@
       </c>
       <c r="I12" s="27"/>
     </row>
-    <row r="13" ht="56" customHeight="1">
+    <row r="13" ht="55.19" customHeight="1">
       <c r="A13" s="0"/>
       <c r="B13" s="21" t="inlineStr">
         <is>
@@ -2797,13 +2797,13 @@
       <c r="C13" s="23"/>
       <c r="D13" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="E13" s="23"/>
       <c r="F13" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="G13" s="23" t="inlineStr">
@@ -2818,11 +2818,11 @@
       </c>
       <c r="I13" s="28"/>
     </row>
-    <row r="14" ht="56" customHeight="1">
+    <row r="14" ht="55.19" customHeight="1">
       <c r="A14" s="0"/>
       <c r="B14" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="C14" s="26"/>
@@ -2835,7 +2835,7 @@
       <c r="E14" s="26"/>
       <c r="F14" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="G14" s="26"/>

--- a/sheets/민요/검수/쑥대머리 (중모리).xlsx
+++ b/sheets/민요/검수/쑥대머리 (중모리).xlsx
@@ -2540,7 +2540,8 @@
       </c>
       <c r="G5" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">항아</t>
+          <t xml:space="preserve">항
+아</t>
         </is>
       </c>
       <c r="H5" s="21" t="inlineStr">
@@ -2550,7 +2551,8 @@
       </c>
       <c r="I5" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">신혼</t>
+          <t xml:space="preserve">신
+혼</t>
         </is>
       </c>
     </row>
@@ -2653,7 +2655,8 @@
       </c>
       <c r="C9" s="27" t="inlineStr">
         <is>
-          <t xml:space="preserve">막혀</t>
+          <t xml:space="preserve">막
+혀</t>
         </is>
       </c>
       <c r="D9" s="21" t="inlineStr">
@@ -2695,7 +2698,8 @@
       </c>
       <c r="C10" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">막혀</t>
+          <t xml:space="preserve">막
+혀</t>
         </is>
       </c>
       <c r="D10" s="21" t="inlineStr">

--- a/sheets/민요/검수/쑥대머리 (중모리).xlsx
+++ b/sheets/민요/검수/쑥대머리 (중모리).xlsx
@@ -11,7 +11,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="7">
+  <fonts count="8">
     <font>
       <sz val="11"/>
       <name val="궁서체"/>
@@ -47,6 +47,11 @@
     </font>
     <font>
       <sz val="12"/>
+      <name val="궁서체"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="18"/>
       <name val="궁서체"/>
       <family val="2"/>
     </font>
@@ -150,7 +155,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="35">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -234,6 +239,24 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -2432,7 +2455,7 @@
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="C3" s="22" t="inlineStr">
+      <c r="C3" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">막</t>
         </is>
@@ -2443,7 +2466,7 @@
 潢</t>
         </is>
       </c>
-      <c r="E3" s="22" t="inlineStr">
+      <c r="E3" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">번</t>
         </is>
@@ -2453,7 +2476,7 @@
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="G3" s="22" t="inlineStr">
+      <c r="G3" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">계</t>
         </is>
@@ -2464,7 +2487,7 @@
 潢潢</t>
         </is>
       </c>
-      <c r="I3" s="22" t="inlineStr">
+      <c r="I3" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">예</t>
         </is>
@@ -2477,7 +2500,7 @@
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="C4" s="23" t="inlineStr">
+      <c r="C4" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">왕</t>
         </is>
@@ -2487,7 +2510,7 @@
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="E4" s="23" t="inlineStr">
+      <c r="E4" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">듯</t>
         </is>
@@ -2498,7 +2521,7 @@
 南</t>
         </is>
       </c>
-      <c r="G4" s="23" t="inlineStr">
+      <c r="G4" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">궁</t>
         </is>
@@ -2508,7 +2531,7 @@
           <t xml:space="preserve">潢潢</t>
         </is>
       </c>
-      <c r="I4" s="23" t="inlineStr">
+      <c r="I4" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">의</t>
         </is>
@@ -2522,13 +2545,13 @@
 潢</t>
         </is>
       </c>
-      <c r="C5" s="25"/>
+      <c r="C5" s="31"/>
       <c r="D5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="E5" s="26" t="inlineStr">
+      <c r="E5" s="32" t="inlineStr">
         <is>
           <t xml:space="preserve">이</t>
         </is>
@@ -2538,7 +2561,7 @@
           <t xml:space="preserve">南南</t>
         </is>
       </c>
-      <c r="G5" s="26" t="inlineStr">
+      <c r="G5" s="32" t="inlineStr">
         <is>
           <t xml:space="preserve">항
 아</t>
@@ -2549,7 +2572,7 @@
           <t xml:space="preserve">潢潢</t>
         </is>
       </c>
-      <c r="I5" s="26" t="inlineStr">
+      <c r="I5" s="32" t="inlineStr">
         <is>
           <t xml:space="preserve">신
 혼</t>
@@ -2564,25 +2587,25 @@
 △</t>
         </is>
       </c>
-      <c r="C6" s="27"/>
+      <c r="C6" s="33"/>
       <c r="D6" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">△</t>
         </is>
       </c>
-      <c r="E6" s="22"/>
+      <c r="E6" s="29"/>
       <c r="F6" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="G6" s="22"/>
+      <c r="G6" s="29"/>
       <c r="H6" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢潢</t>
         </is>
       </c>
-      <c r="I6" s="22"/>
+      <c r="I6" s="29"/>
     </row>
     <row r="7" ht="55.19" customHeight="1">
       <c r="A7" s="0"/>
@@ -2591,7 +2614,7 @@
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="C7" s="23" t="inlineStr">
+      <c r="C7" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">막</t>
         </is>
@@ -2601,19 +2624,19 @@
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="E7" s="23"/>
+      <c r="E7" s="30"/>
       <c r="F7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="G7" s="23"/>
+      <c r="G7" s="30"/>
       <c r="H7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="I7" s="23"/>
+      <c r="I7" s="30"/>
     </row>
     <row r="8" ht="55.19" customHeight="1">
       <c r="A8" s="0"/>
@@ -2623,27 +2646,27 @@
 潢</t>
         </is>
       </c>
-      <c r="C8" s="25"/>
+      <c r="C8" s="31"/>
       <c r="D8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 姑</t>
         </is>
       </c>
-      <c r="E8" s="26"/>
+      <c r="E8" s="32"/>
       <c r="F8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 △</t>
         </is>
       </c>
-      <c r="G8" s="26"/>
+      <c r="G8" s="32"/>
       <c r="H8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="I8" s="26"/>
+      <c r="I8" s="32"/>
     </row>
     <row r="9" ht="55.19" customHeight="1">
       <c r="A9" s="0"/>
@@ -2653,7 +2676,7 @@
 姑</t>
         </is>
       </c>
-      <c r="C9" s="27" t="inlineStr">
+      <c r="C9" s="33" t="inlineStr">
         <is>
           <t xml:space="preserve">막
 혀</t>
@@ -2665,7 +2688,7 @@
 南</t>
         </is>
       </c>
-      <c r="E9" s="22" t="inlineStr">
+      <c r="E9" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">비</t>
         </is>
@@ -2676,7 +2699,7 @@
 姑</t>
         </is>
       </c>
-      <c r="G9" s="27" t="inlineStr">
+      <c r="G9" s="33" t="inlineStr">
         <is>
           <t xml:space="preserve">추</t>
         </is>
@@ -2687,7 +2710,7 @@
 潢汰</t>
         </is>
       </c>
-      <c r="I9" s="22"/>
+      <c r="I9" s="29"/>
     </row>
     <row r="10" ht="55.19" customHeight="1">
       <c r="A10" s="0"/>
@@ -2696,7 +2719,7 @@
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="C10" s="23" t="inlineStr">
+      <c r="C10" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">막
 혀</t>
@@ -2707,7 +2730,7 @@
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="E10" s="23" t="inlineStr">
+      <c r="E10" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">치</t>
         </is>
@@ -2717,13 +2740,13 @@
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="G10" s="23"/>
+      <c r="G10" s="30"/>
       <c r="H10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢汰</t>
         </is>
       </c>
-      <c r="I10" s="23"/>
+      <c r="I10" s="30"/>
     </row>
     <row r="11" ht="55.19" customHeight="1">
       <c r="A11" s="0"/>
@@ -2732,7 +2755,7 @@
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="C11" s="26" t="inlineStr">
+      <c r="C11" s="32" t="inlineStr">
         <is>
           <t xml:space="preserve">니</t>
         </is>
@@ -2742,19 +2765,19 @@
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="E11" s="25"/>
+      <c r="E11" s="31"/>
       <c r="F11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="G11" s="26"/>
+      <c r="G11" s="32"/>
       <c r="H11" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">／</t>
         </is>
       </c>
-      <c r="I11" s="25"/>
+      <c r="I11" s="31"/>
     </row>
     <row r="12" ht="55.19" customHeight="1">
       <c r="A12" s="0"/>
@@ -2763,7 +2786,7 @@
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="C12" s="22" t="inlineStr">
+      <c r="C12" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">니</t>
         </is>
@@ -2773,13 +2796,13 @@
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="E12" s="22"/>
+      <c r="E12" s="29"/>
       <c r="F12" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="G12" s="22" t="inlineStr">
+      <c r="G12" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">갈</t>
         </is>
@@ -2789,7 +2812,7 @@
           <t xml:space="preserve">潢潢</t>
         </is>
       </c>
-      <c r="I12" s="27"/>
+      <c r="I12" s="33"/>
     </row>
     <row r="13" ht="55.19" customHeight="1">
       <c r="A13" s="0"/>
@@ -2798,19 +2821,19 @@
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="C13" s="23"/>
+      <c r="C13" s="30"/>
       <c r="D13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="E13" s="23"/>
+      <c r="E13" s="30"/>
       <c r="F13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="G13" s="23" t="inlineStr">
+      <c r="G13" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">이</t>
         </is>
@@ -2820,7 +2843,7 @@
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="I13" s="28"/>
+      <c r="I13" s="34"/>
     </row>
     <row r="14" ht="55.19" customHeight="1">
       <c r="A14" s="0"/>
@@ -2829,26 +2852,26 @@
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="C14" s="26"/>
+      <c r="C14" s="32"/>
       <c r="D14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 △</t>
         </is>
       </c>
-      <c r="E14" s="26"/>
+      <c r="E14" s="32"/>
       <c r="F14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="G14" s="26"/>
+      <c r="G14" s="32"/>
       <c r="H14" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="I14" s="25"/>
+      <c r="I14" s="31"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/sheets/민요/검수/쑥대머리 (중모리).xlsx
+++ b/sheets/민요/검수/쑥대머리 (중모리).xlsx
@@ -11,7 +11,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="8">
+  <fonts count="7">
     <font>
       <sz val="11"/>
       <name val="궁서체"/>
@@ -42,11 +42,6 @@
     </font>
     <font>
       <sz val="24"/>
-      <name val="궁서체"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="12"/>
       <name val="궁서체"/>
       <family val="2"/>
     </font>
@@ -155,7 +150,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="35">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -223,40 +218,22 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -353,7 +330,7 @@
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">48</t>
+          <t xml:space="preserve">60</t>
         </is>
       </c>
     </row>
@@ -365,7 +342,7 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
     </row>
@@ -389,7 +366,7 @@
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">중</t>
+          <t xml:space="preserve">상</t>
         </is>
       </c>
     </row>
@@ -399,11 +376,7 @@
           <t xml:space="preserve">확인 필요</t>
         </is>
       </c>
-      <c r="B12" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">비고 21%</t>
-        </is>
-      </c>
+      <c r="B12" s="4"/>
     </row>
     <row r="13">
       <c r="A13" s="0"/>
@@ -429,7 +402,7 @@
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">12정간, 굵은 선 3칸마다. 오른쪽 여백 "&lt;ス&gt;" 표시, 부제 "중모리". 4줄 사용(5~8줄 빈칸). "- 197 -"는 양식 용지 번호. 하단 메모칸 "※ 潢 ⇒ 無"(판독자 교정 지시). 청성(氵)이 많아 潢·淋 다수. 검수: 2·3·4줄 정간 정렬 재판독(원래 초안의 3줄은 2줄 중복, 4줄은 1행 밀림이었음).</t>
+          <t xml:space="preserve">10-13 전면 재판독. 12정간(굵은 선 3칸마다), 5줄 사용(6~8줄 빈칸). 오른쪽 여백 "&lt;ス&gt;" 쑥대머리 중모리. 潢 뒤 이중 곡선 꼬리는 ^ 로 표기 — 하단 메모 "※ 潢(꼬리) ⇒ 潢→無"(꼬리 = 無로 흘러내림 표시). (無)는 괄호 친 無. "- 197 -"는 양식 용지 번호.</t>
         </is>
       </c>
     </row>
@@ -615,23 +588,27 @@
       <c r="F2" s="2">
         <v>1</v>
       </c>
-      <c r="G2" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑|潢潢</t>
-        </is>
-      </c>
-      <c r="H2" s="2" t="inlineStr">
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑|潢</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
-潢潢</t>
-        </is>
-      </c>
-      <c r="I2" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">예</t>
-        </is>
-      </c>
-      <c r="J2" s="4"/>
+潢</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">예의</t>
+        </is>
+      </c>
+      <c r="J2" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">위 姑 변 없음으로 판독(㴌?)</t>
+        </is>
+      </c>
       <c r="K2" s="2"/>
     </row>
     <row r="3">
@@ -657,17 +634,18 @@
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢潢</t>
+          <t xml:space="preserve">潢|潢</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢潢</t>
+          <t xml:space="preserve">潢
+潢</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">의</t>
+          <t xml:space="preserve">신혼</t>
         </is>
       </c>
       <c r="J3" s="4"/>
@@ -696,17 +674,18 @@
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢潢</t>
+          <t xml:space="preserve">潢|潢</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢潢</t>
+          <t xml:space="preserve">潢
+潢</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">신혼</t>
+          <t xml:space="preserve">금술</t>
         </is>
       </c>
       <c r="J4" s="4"/>
@@ -735,15 +714,20 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢潢</t>
+          <t xml:space="preserve">潢|潢</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢潢</t>
-        </is>
-      </c>
-      <c r="I5" s="2"/>
+          <t xml:space="preserve">潢
+潢</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">위지</t>
+        </is>
+      </c>
       <c r="J5" s="4"/>
       <c r="K5" s="2"/>
     </row>
@@ -770,12 +754,12 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I6" s="2"/>
@@ -805,12 +789,12 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢</t>
+          <t xml:space="preserve">潢^</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢</t>
+          <t xml:space="preserve">潢^</t>
         </is>
       </c>
       <c r="I7" s="2"/>
@@ -840,16 +824,20 @@
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢汰|潢汰</t>
+          <t xml:space="preserve">潢|㴌</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢汰
-潢汰</t>
-        </is>
-      </c>
-      <c r="I8" s="2"/>
+          <t xml:space="preserve">潢
+㴌</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">나를</t>
+        </is>
+      </c>
       <c r="J8" s="4"/>
       <c r="K8" s="2"/>
     </row>
@@ -876,15 +864,20 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢汰</t>
+          <t xml:space="preserve">㴌|㴌</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢汰</t>
-        </is>
-      </c>
-      <c r="I9" s="2"/>
+          <t xml:space="preserve">㴌
+㴌</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">잃고</t>
+        </is>
+      </c>
       <c r="J9" s="4"/>
       <c r="K9" s="2"/>
     </row>
@@ -911,18 +904,19 @@
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">／</t>
+          <t xml:space="preserve">–|ﾉ</t>
         </is>
       </c>
       <c r="H10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">／</t>
+          <t xml:space="preserve">–
+ﾉ</t>
         </is>
       </c>
       <c r="I10" s="3"/>
       <c r="J10" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">율명 앞 사선 모양</t>
+          <t xml:space="preserve">–아래 길게 내려긋는 곡선</t>
         </is>
       </c>
       <c r="K10" s="2"/>
@@ -948,22 +942,23 @@
       <c r="F11" s="2">
         <v>4</v>
       </c>
-      <c r="G11" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢潢</t>
-        </is>
-      </c>
-      <c r="H11" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢潢</t>
-        </is>
-      </c>
-      <c r="I11" s="3"/>
-      <c r="J11" s="4" t="inlineStr">
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢^|潢^</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢^
+潢^</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">어러</t>
         </is>
       </c>
+      <c r="J11" s="4"/>
       <c r="K11" s="2"/>
     </row>
     <row r="12">
@@ -987,22 +982,22 @@
       <c r="F12" s="2">
         <v>4</v>
       </c>
-      <c r="G12" s="3" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="H12" s="3" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="I12" s="3"/>
-      <c r="J12" s="4" t="inlineStr">
+      <c r="I12" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">는</t>
         </is>
       </c>
+      <c r="J12" s="4"/>
       <c r="K12" s="2"/>
     </row>
     <row r="13">
@@ -1026,22 +1021,22 @@
       <c r="F13" s="2">
         <v>4</v>
       </c>
-      <c r="G13" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢</t>
-        </is>
-      </c>
-      <c r="H13" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢</t>
-        </is>
-      </c>
-      <c r="I13" s="3"/>
-      <c r="J13" s="4" t="inlineStr">
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢^</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢^</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">가</t>
         </is>
       </c>
+      <c r="J13" s="4"/>
       <c r="K13" s="2"/>
     </row>
     <row r="14">
@@ -1146,12 +1141,13 @@
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">南南</t>
+          <t xml:space="preserve">南|南</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">南南</t>
+          <t xml:space="preserve">南
+南</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1220,12 +1216,12 @@
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I18" s="2"/>
@@ -1289,27 +1285,23 @@
       <c r="F20" s="2">
         <v>3</v>
       </c>
-      <c r="G20" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢潢|姑</t>
-        </is>
-      </c>
-      <c r="H20" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢潢
-姑</t>
-        </is>
-      </c>
-      <c r="I20" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">추</t>
-        </is>
-      </c>
-      <c r="J20" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">氵계열 두 글자+姑</t>
-        </is>
-      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">㴌|潢^</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">㴌
+潢^</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">추월</t>
+        </is>
+      </c>
+      <c r="J20" s="4"/>
       <c r="K20" s="2"/>
     </row>
     <row r="21">
@@ -1335,12 +1327,12 @@
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">姑</t>
+          <t xml:space="preserve">㴌</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">姑</t>
+          <t xml:space="preserve">㴌</t>
         </is>
       </c>
       <c r="I21" s="2"/>
@@ -1370,12 +1362,12 @@
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">南</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">南</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I22" s="2"/>
@@ -1405,19 +1397,16 @@
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">南</t>
+          <t xml:space="preserve">·|△</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">南</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">갈</t>
-        </is>
-      </c>
+          <t xml:space="preserve">·
+△</t>
+        </is>
+      </c>
+      <c r="I23" s="2"/>
       <c r="J23" s="4"/>
       <c r="K23" s="2"/>
     </row>
@@ -1444,17 +1433,17 @@
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">㴌</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">㴌</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">이</t>
+          <t xml:space="preserve">같</t>
         </is>
       </c>
       <c r="J24" s="4"/>
@@ -1483,15 +1472,19 @@
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">潢^</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="I25" s="2"/>
+          <t xml:space="preserve">潢^</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">이</t>
+        </is>
+      </c>
       <c r="J25" s="4"/>
       <c r="K25" s="2"/>
     </row>
@@ -1518,13 +1511,12 @@
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">南|潢</t>
+          <t xml:space="preserve">南</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">南
-潢</t>
+          <t xml:space="preserve">南</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -1558,19 +1550,15 @@
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="I27" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">듯</t>
-        </is>
-      </c>
+          <t xml:space="preserve">–</t>
+        </is>
+      </c>
+      <c r="I27" s="2"/>
       <c r="J27" s="4"/>
       <c r="K27" s="2"/>
     </row>
@@ -1597,17 +1585,18 @@
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">–</t>
+          <t xml:space="preserve">湳|湳</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">–</t>
+          <t xml:space="preserve">湳
+湳</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">이</t>
+          <t xml:space="preserve">듯이</t>
         </is>
       </c>
       <c r="J28" s="4"/>
@@ -1636,15 +1625,20 @@
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">△</t>
+          <t xml:space="preserve">㴌|潢^</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">△</t>
-        </is>
-      </c>
-      <c r="I29" s="2"/>
+          <t xml:space="preserve">㴌
+潢^</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">솟아</t>
+        </is>
+      </c>
       <c r="J29" s="4"/>
       <c r="K29" s="2"/>
     </row>
@@ -1669,18 +1663,26 @@
       <c r="F30" s="2">
         <v>2</v>
       </c>
-      <c r="G30" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢</t>
-        </is>
-      </c>
-      <c r="H30" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢</t>
-        </is>
-      </c>
-      <c r="I30" s="2"/>
-      <c r="J30" s="4"/>
+      <c r="G30" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">無</t>
+        </is>
+      </c>
+      <c r="H30" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">無</t>
+        </is>
+      </c>
+      <c r="I30" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">아</t>
+        </is>
+      </c>
+      <c r="J30" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">괄호 친 (無)</t>
+        </is>
+      </c>
       <c r="K30" s="2"/>
     </row>
     <row r="31">
@@ -1706,16 +1708,20 @@
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢|姑</t>
+          <t xml:space="preserve">南|△</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢
-姑</t>
-        </is>
-      </c>
-      <c r="I31" s="2"/>
+          <t xml:space="preserve">南
+△</t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">서</t>
+        </is>
+      </c>
       <c r="J31" s="4"/>
       <c r="K31" s="2"/>
     </row>
@@ -1742,18 +1748,18 @@
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢|南</t>
+          <t xml:space="preserve">潢^|姑</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢
-南</t>
+          <t xml:space="preserve">潢^
+姑</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">비</t>
+          <t xml:space="preserve">비치</t>
         </is>
       </c>
       <c r="J32" s="4"/>
@@ -1782,17 +1788,17 @@
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">姑</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">姑</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">치</t>
+          <t xml:space="preserve">이</t>
         </is>
       </c>
       <c r="J33" s="4"/>
@@ -1819,22 +1825,22 @@
       <c r="F34" s="2">
         <v>3</v>
       </c>
-      <c r="G34" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="H34" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="I34" s="3"/>
-      <c r="J34" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">이</t>
-        </is>
-      </c>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">고</t>
+        </is>
+      </c>
+      <c r="J34" s="4"/>
       <c r="K34" s="2"/>
     </row>
     <row r="35">
@@ -1860,15 +1866,19 @@
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">姑</t>
+          <t xml:space="preserve">南</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="I35" s="2"/>
+          <t xml:space="preserve">南</t>
+        </is>
+      </c>
+      <c r="I35" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">저</t>
+        </is>
+      </c>
       <c r="J35" s="4"/>
       <c r="K35" s="2"/>
     </row>
@@ -1895,12 +1905,12 @@
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I36" s="2"/>
@@ -1930,13 +1940,12 @@
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">–|△</t>
+          <t xml:space="preserve">△</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">–
-△</t>
+          <t xml:space="preserve">△</t>
         </is>
       </c>
       <c r="I37" s="2"/>
@@ -1966,17 +1975,18 @@
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">南</t>
+          <t xml:space="preserve">南|湳</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">南</t>
+          <t xml:space="preserve">南
+湳</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">막</t>
+          <t xml:space="preserve">막왕</t>
         </is>
       </c>
       <c r="J38" s="4"/>
@@ -2005,19 +2015,15 @@
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢</t>
+          <t xml:space="preserve">·</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢</t>
-        </is>
-      </c>
-      <c r="I39" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">왕</t>
-        </is>
-      </c>
+          <t xml:space="preserve">·</t>
+        </is>
+      </c>
+      <c r="I39" s="2"/>
       <c r="J39" s="4"/>
       <c r="K39" s="2"/>
     </row>
@@ -2042,23 +2048,18 @@
       <c r="F40" s="2">
         <v>1</v>
       </c>
-      <c r="G40" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">淋|潢</t>
-        </is>
-      </c>
-      <c r="H40" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">淋
-潢</t>
-        </is>
-      </c>
-      <c r="I40" s="3"/>
-      <c r="J40" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">막왕</t>
-        </is>
-      </c>
+      <c r="G40" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–</t>
+        </is>
+      </c>
+      <c r="H40" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–</t>
+        </is>
+      </c>
+      <c r="I40" s="2"/>
+      <c r="J40" s="4"/>
       <c r="K40" s="2"/>
     </row>
     <row r="41">
@@ -2082,23 +2083,18 @@
       <c r="F41" s="2">
         <v>2</v>
       </c>
-      <c r="G41" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">無|△</t>
-        </is>
-      </c>
-      <c r="H41" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">無
-△</t>
-        </is>
-      </c>
-      <c r="I41" s="3"/>
-      <c r="J41" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">괄호로 둘러싼 無, 아래 △</t>
-        </is>
-      </c>
+      <c r="G41" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">△</t>
+        </is>
+      </c>
+      <c r="H41" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">△</t>
+        </is>
+      </c>
+      <c r="I41" s="2"/>
+      <c r="J41" s="4"/>
       <c r="K41" s="2"/>
     </row>
     <row r="42">
@@ -2124,12 +2120,12 @@
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">南</t>
+          <t xml:space="preserve">湳</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">南</t>
+          <t xml:space="preserve">湳</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
@@ -2161,23 +2157,22 @@
       <c r="F43" s="2">
         <v>2</v>
       </c>
-      <c r="G43" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">–|潢</t>
-        </is>
-      </c>
-      <c r="H43" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">–
-潢</t>
-        </is>
-      </c>
-      <c r="I43" s="3"/>
-      <c r="J43" s="4" t="inlineStr">
+      <c r="G43" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">㴌</t>
+        </is>
+      </c>
+      <c r="H43" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">㴌</t>
+        </is>
+      </c>
+      <c r="I43" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">래</t>
         </is>
       </c>
+      <c r="J43" s="4"/>
       <c r="K43" s="2"/>
     </row>
     <row r="44">
@@ -2201,27 +2196,23 @@
       <c r="F44" s="2">
         <v>3</v>
       </c>
-      <c r="G44" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢潢|姑</t>
-        </is>
-      </c>
-      <c r="H44" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢潢
-姑</t>
-        </is>
-      </c>
-      <c r="I44" s="3" t="inlineStr">
+      <c r="G44" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢^|南</t>
+        </is>
+      </c>
+      <c r="H44" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢^
+南</t>
+        </is>
+      </c>
+      <c r="I44" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">막혀</t>
         </is>
       </c>
-      <c r="J44" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">氵계열 두 글자+姑</t>
-        </is>
-      </c>
+      <c r="J44" s="4"/>
       <c r="K44" s="2"/>
     </row>
     <row r="45">
@@ -2247,19 +2238,15 @@
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">姑</t>
+          <t xml:space="preserve">·</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="I45" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">막혀</t>
-        </is>
-      </c>
+          <t xml:space="preserve">·</t>
+        </is>
+      </c>
+      <c r="I45" s="2"/>
       <c r="J45" s="4"/>
       <c r="K45" s="2"/>
     </row>
@@ -2286,17 +2273,17 @@
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">南</t>
+          <t xml:space="preserve">姑</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">南</t>
+          <t xml:space="preserve">姑</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">니</t>
+          <t xml:space="preserve">으</t>
         </is>
       </c>
       <c r="J46" s="4"/>
@@ -2325,12 +2312,12 @@
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">南</t>
+          <t xml:space="preserve">姑</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">南</t>
+          <t xml:space="preserve">姑</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
@@ -2364,12 +2351,12 @@
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">–</t>
+          <t xml:space="preserve">·</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">–</t>
+          <t xml:space="preserve">·</t>
         </is>
       </c>
       <c r="I48" s="2"/>
@@ -2399,20 +2386,494 @@
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–|△</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–
+△</t>
         </is>
       </c>
       <c r="I49" s="2"/>
       <c r="J49" s="4"/>
       <c r="K49" s="2"/>
     </row>
+    <row r="50">
+      <c r="A50" s="2">
+        <v>1</v>
+      </c>
+      <c r="B50" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">민요채보-1/쑥대머리-2.png</t>
+        </is>
+      </c>
+      <c r="C50" s="2">
+        <v>5</v>
+      </c>
+      <c r="D50" s="2">
+        <v>5</v>
+      </c>
+      <c r="E50" s="2">
+        <v>1</v>
+      </c>
+      <c r="F50" s="2">
+        <v>1</v>
+      </c>
+      <c r="G50" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南</t>
+        </is>
+      </c>
+      <c r="H50" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南</t>
+        </is>
+      </c>
+      <c r="I50" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">앵</t>
+        </is>
+      </c>
+      <c r="J50" s="4"/>
+      <c r="K50" s="2"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="2">
+        <v>1</v>
+      </c>
+      <c r="B51" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">민요채보-1/쑥대머리-2.png</t>
+        </is>
+      </c>
+      <c r="C51" s="2">
+        <v>5</v>
+      </c>
+      <c r="D51" s="2">
+        <v>5</v>
+      </c>
+      <c r="E51" s="2">
+        <v>2</v>
+      </c>
+      <c r="F51" s="2">
+        <v>1</v>
+      </c>
+      <c r="G51" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢^</t>
+        </is>
+      </c>
+      <c r="H51" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢^</t>
+        </is>
+      </c>
+      <c r="I51" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">무</t>
+        </is>
+      </c>
+      <c r="J51" s="4"/>
+      <c r="K51" s="2"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="2">
+        <v>1</v>
+      </c>
+      <c r="B52" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">민요채보-1/쑥대머리-2.png</t>
+        </is>
+      </c>
+      <c r="C52" s="2">
+        <v>5</v>
+      </c>
+      <c r="D52" s="2">
+        <v>5</v>
+      </c>
+      <c r="E52" s="2">
+        <v>3</v>
+      </c>
+      <c r="F52" s="2">
+        <v>1</v>
+      </c>
+      <c r="G52" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">㴌|潢^</t>
+        </is>
+      </c>
+      <c r="H52" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">㴌
+潢^</t>
+        </is>
+      </c>
+      <c r="I52" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">서를</t>
+        </is>
+      </c>
+      <c r="J52" s="4"/>
+      <c r="K52" s="2"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="2">
+        <v>1</v>
+      </c>
+      <c r="B53" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">민요채보-1/쑥대머리-2.png</t>
+        </is>
+      </c>
+      <c r="C53" s="2">
+        <v>5</v>
+      </c>
+      <c r="D53" s="2">
+        <v>5</v>
+      </c>
+      <c r="E53" s="2">
+        <v>4</v>
+      </c>
+      <c r="F53" s="2">
+        <v>2</v>
+      </c>
+      <c r="G53" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">無|△</t>
+        </is>
+      </c>
+      <c r="H53" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">無
+△</t>
+        </is>
+      </c>
+      <c r="I53" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">을</t>
+        </is>
+      </c>
+      <c r="J53" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">괄호 친 (無), 위 潢 꼬리가 이어짐</t>
+        </is>
+      </c>
+      <c r="K53" s="2"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="2">
+        <v>1</v>
+      </c>
+      <c r="B54" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">민요채보-1/쑥대머리-2.png</t>
+        </is>
+      </c>
+      <c r="C54" s="2">
+        <v>5</v>
+      </c>
+      <c r="D54" s="2">
+        <v>5</v>
+      </c>
+      <c r="E54" s="2">
+        <v>5</v>
+      </c>
+      <c r="F54" s="2">
+        <v>2</v>
+      </c>
+      <c r="G54" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南</t>
+        </is>
+      </c>
+      <c r="H54" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南</t>
+        </is>
+      </c>
+      <c r="I54" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">네</t>
+        </is>
+      </c>
+      <c r="J54" s="4"/>
+      <c r="K54" s="2"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="2">
+        <v>1</v>
+      </c>
+      <c r="B55" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">민요채보-1/쑥대머리-2.png</t>
+        </is>
+      </c>
+      <c r="C55" s="2">
+        <v>5</v>
+      </c>
+      <c r="D55" s="2">
+        <v>5</v>
+      </c>
+      <c r="E55" s="2">
+        <v>6</v>
+      </c>
+      <c r="F55" s="2">
+        <v>2</v>
+      </c>
+      <c r="G55" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–|潢^</t>
+        </is>
+      </c>
+      <c r="H55" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–
+潢^</t>
+        </is>
+      </c>
+      <c r="I55" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">가</t>
+        </is>
+      </c>
+      <c r="J55" s="4"/>
+      <c r="K55" s="2"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="2">
+        <v>1</v>
+      </c>
+      <c r="B56" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">민요채보-1/쑥대머리-2.png</t>
+        </is>
+      </c>
+      <c r="C56" s="2">
+        <v>5</v>
+      </c>
+      <c r="D56" s="2">
+        <v>5</v>
+      </c>
+      <c r="E56" s="2">
+        <v>7</v>
+      </c>
+      <c r="F56" s="2">
+        <v>3</v>
+      </c>
+      <c r="G56" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">㴌|姑</t>
+        </is>
+      </c>
+      <c r="H56" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">㴌
+姑</t>
+        </is>
+      </c>
+      <c r="I56" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">못봤</t>
+        </is>
+      </c>
+      <c r="J56" s="4"/>
+      <c r="K56" s="2"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="2">
+        <v>1</v>
+      </c>
+      <c r="B57" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">민요채보-1/쑥대머리-2.png</t>
+        </is>
+      </c>
+      <c r="C57" s="2">
+        <v>5</v>
+      </c>
+      <c r="D57" s="2">
+        <v>5</v>
+      </c>
+      <c r="E57" s="2">
+        <v>8</v>
+      </c>
+      <c r="F57" s="2">
+        <v>3</v>
+      </c>
+      <c r="G57" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="H57" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="I57" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">앗</t>
+        </is>
+      </c>
+      <c r="J57" s="4"/>
+      <c r="K57" s="2"/>
+    </row>
+    <row r="58">
+      <c r="A58" s="2">
+        <v>1</v>
+      </c>
+      <c r="B58" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">민요채보-1/쑥대머리-2.png</t>
+        </is>
+      </c>
+      <c r="C58" s="2">
+        <v>5</v>
+      </c>
+      <c r="D58" s="2">
+        <v>5</v>
+      </c>
+      <c r="E58" s="2">
+        <v>9</v>
+      </c>
+      <c r="F58" s="2">
+        <v>3</v>
+      </c>
+      <c r="G58" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南</t>
+        </is>
+      </c>
+      <c r="H58" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南</t>
+        </is>
+      </c>
+      <c r="I58" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">으</t>
+        </is>
+      </c>
+      <c r="J58" s="4"/>
+      <c r="K58" s="2"/>
+    </row>
+    <row r="59">
+      <c r="A59" s="2">
+        <v>1</v>
+      </c>
+      <c r="B59" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">민요채보-1/쑥대머리-2.png</t>
+        </is>
+      </c>
+      <c r="C59" s="2">
+        <v>5</v>
+      </c>
+      <c r="D59" s="2">
+        <v>5</v>
+      </c>
+      <c r="E59" s="2">
+        <v>10</v>
+      </c>
+      <c r="F59" s="2">
+        <v>4</v>
+      </c>
+      <c r="G59" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南</t>
+        </is>
+      </c>
+      <c r="H59" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南</t>
+        </is>
+      </c>
+      <c r="I59" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">니</t>
+        </is>
+      </c>
+      <c r="J59" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">가사 4처럼 보임, 니로 판독</t>
+        </is>
+      </c>
+      <c r="K59" s="2"/>
+    </row>
+    <row r="60">
+      <c r="A60" s="2">
+        <v>1</v>
+      </c>
+      <c r="B60" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">민요채보-1/쑥대머리-2.png</t>
+        </is>
+      </c>
+      <c r="C60" s="2">
+        <v>5</v>
+      </c>
+      <c r="D60" s="2">
+        <v>5</v>
+      </c>
+      <c r="E60" s="2">
+        <v>11</v>
+      </c>
+      <c r="F60" s="2">
+        <v>4</v>
+      </c>
+      <c r="G60" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–</t>
+        </is>
+      </c>
+      <c r="H60" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–</t>
+        </is>
+      </c>
+      <c r="I60" s="2"/>
+      <c r="J60" s="4"/>
+      <c r="K60" s="2"/>
+    </row>
+    <row r="61">
+      <c r="A61" s="2">
+        <v>1</v>
+      </c>
+      <c r="B61" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">민요채보-1/쑥대머리-2.png</t>
+        </is>
+      </c>
+      <c r="C61" s="2">
+        <v>5</v>
+      </c>
+      <c r="D61" s="2">
+        <v>5</v>
+      </c>
+      <c r="E61" s="2">
+        <v>12</v>
+      </c>
+      <c r="F61" s="2">
+        <v>4</v>
+      </c>
+      <c r="G61" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–|△</t>
+        </is>
+      </c>
+      <c r="H61" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–
+△</t>
+        </is>
+      </c>
+      <c r="I61" s="2"/>
+      <c r="J61" s="4"/>
+      <c r="K61" s="2"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:K49"/>
+  <autoFilter ref="A1:K61"/>
 </worksheet>
 </file>
 
@@ -2428,12 +2889,14 @@
     <col min="7" max="7" width="6" customWidth="1"/>
     <col min="8" max="8" width="12" customWidth="1"/>
     <col min="9" max="9" width="6" customWidth="1"/>
+    <col min="10" max="10" width="12" customWidth="1"/>
+    <col min="11" max="11" width="6" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="0"/>
     </row>
-    <row r="2" ht="55.19" customHeight="1">
+    <row r="2" ht="59.7" customHeight="1">
       <c r="A2" s="0"/>
       <c r="B2" s="20" t="inlineStr">
         <is>
@@ -2447,62 +2910,76 @@
       <c r="G2" s="20"/>
       <c r="H2" s="20"/>
       <c r="I2" s="20"/>
-    </row>
-    <row r="3" ht="55.19" customHeight="1">
+      <c r="J2" s="20"/>
+      <c r="K2" s="20"/>
+    </row>
+    <row r="3" ht="59.7" customHeight="1">
       <c r="A3" s="0"/>
       <c r="B3" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="C3" s="29" t="inlineStr">
-        <is>
-          <t xml:space="preserve">막</t>
+      <c r="C3" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">앵</t>
         </is>
       </c>
       <c r="D3" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南
+湳</t>
+        </is>
+      </c>
+      <c r="E3" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">막
+왕</t>
+        </is>
+      </c>
+      <c r="F3" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南</t>
+        </is>
+      </c>
+      <c r="G3" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">번</t>
+        </is>
+      </c>
+      <c r="H3" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="I3" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">계</t>
+        </is>
+      </c>
+      <c r="J3" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑
 潢</t>
         </is>
       </c>
-      <c r="E3" s="29" t="inlineStr">
-        <is>
-          <t xml:space="preserve">번</t>
-        </is>
-      </c>
-      <c r="F3" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="G3" s="29" t="inlineStr">
-        <is>
-          <t xml:space="preserve">계</t>
-        </is>
-      </c>
-      <c r="H3" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑
-潢潢</t>
-        </is>
-      </c>
-      <c r="I3" s="29" t="inlineStr">
-        <is>
-          <t xml:space="preserve">예</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="55.19" customHeight="1">
+      <c r="K3" s="24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">예
+의</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="59.7" customHeight="1">
       <c r="A4" s="0"/>
       <c r="B4" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢</t>
-        </is>
-      </c>
-      <c r="C4" s="30" t="inlineStr">
-        <is>
-          <t xml:space="preserve">왕</t>
+          <t xml:space="preserve">潢^</t>
+        </is>
+      </c>
+      <c r="C4" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">무</t>
         </is>
       </c>
       <c r="D4" s="21" t="inlineStr">
@@ -2510,219 +2987,310 @@
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="E4" s="30" t="inlineStr">
-        <is>
-          <t xml:space="preserve">듯</t>
-        </is>
-      </c>
+      <c r="E4" s="25"/>
       <c r="F4" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–</t>
+        </is>
+      </c>
+      <c r="G4" s="25"/>
+      <c r="H4" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 南</t>
         </is>
       </c>
-      <c r="G4" s="30" t="inlineStr">
+      <c r="I4" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">궁</t>
         </is>
       </c>
-      <c r="H4" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢潢</t>
-        </is>
-      </c>
-      <c r="I4" s="30" t="inlineStr">
-        <is>
-          <t xml:space="preserve">의</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="55.19" customHeight="1">
+      <c r="J4" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢
+潢</t>
+        </is>
+      </c>
+      <c r="K4" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">신
+혼</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="59.7" customHeight="1">
       <c r="A5" s="0"/>
-      <c r="B5" s="24" t="inlineStr">
-        <is>
-          <t xml:space="preserve">淋
-潢</t>
-        </is>
-      </c>
-      <c r="C5" s="31"/>
+      <c r="B5" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">㴌
+潢^</t>
+        </is>
+      </c>
+      <c r="C5" s="26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">서
+를</t>
+        </is>
+      </c>
       <c r="D5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="E5" s="32" t="inlineStr">
-        <is>
-          <t xml:space="preserve">이</t>
-        </is>
-      </c>
+      <c r="E5" s="26"/>
       <c r="F5" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">南南</t>
-        </is>
-      </c>
-      <c r="G5" s="32" t="inlineStr">
+          <t xml:space="preserve">湳
+湳</t>
+        </is>
+      </c>
+      <c r="G5" s="26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">듯
+이</t>
+        </is>
+      </c>
+      <c r="H5" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南
+南</t>
+        </is>
+      </c>
+      <c r="I5" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">항
 아</t>
         </is>
       </c>
-      <c r="H5" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢潢</t>
-        </is>
-      </c>
-      <c r="I5" s="32" t="inlineStr">
-        <is>
-          <t xml:space="preserve">신
-혼</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="55.19" customHeight="1">
+      <c r="J5" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢
+潢</t>
+        </is>
+      </c>
+      <c r="K5" s="26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">금
+술</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="59.7" customHeight="1">
       <c r="A6" s="0"/>
-      <c r="B6" s="24" t="inlineStr">
+      <c r="B6" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 △</t>
         </is>
       </c>
-      <c r="C6" s="33"/>
+      <c r="C6" s="24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">을</t>
+        </is>
+      </c>
       <c r="D6" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">△</t>
         </is>
       </c>
-      <c r="E6" s="29"/>
+      <c r="E6" s="22"/>
       <c r="F6" s="21" t="inlineStr">
         <is>
+          <t xml:space="preserve">㴌
+潢^</t>
+        </is>
+      </c>
+      <c r="G6" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">솟
+아</t>
+        </is>
+      </c>
+      <c r="H6" s="21" t="inlineStr">
+        <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="G6" s="29"/>
-      <c r="H6" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢潢</t>
-        </is>
-      </c>
-      <c r="I6" s="29"/>
-    </row>
-    <row r="7" ht="55.19" customHeight="1">
+      <c r="I6" s="22"/>
+      <c r="J6" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢
+潢</t>
+        </is>
+      </c>
+      <c r="K6" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">위
+지</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="59.7" customHeight="1">
       <c r="A7" s="0"/>
       <c r="B7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="C7" s="30" t="inlineStr">
+      <c r="C7" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">네</t>
+        </is>
+      </c>
+      <c r="D7" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">湳</t>
+        </is>
+      </c>
+      <c r="E7" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">막</t>
         </is>
       </c>
-      <c r="D7" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢</t>
-        </is>
-      </c>
-      <c r="E7" s="30"/>
-      <c r="F7" s="21" t="inlineStr">
+      <c r="F7" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">無</t>
+        </is>
+      </c>
+      <c r="G7" s="27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">아</t>
+        </is>
+      </c>
+      <c r="H7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="G7" s="30"/>
-      <c r="H7" s="21" t="inlineStr">
+      <c r="I7" s="25"/>
+      <c r="J7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="I7" s="30"/>
-    </row>
-    <row r="8" ht="55.19" customHeight="1">
+      <c r="K7" s="25"/>
+    </row>
+    <row r="8" ht="59.7" customHeight="1">
       <c r="A8" s="0"/>
-      <c r="B8" s="24" t="inlineStr">
+      <c r="B8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
-潢</t>
-        </is>
-      </c>
-      <c r="C8" s="31"/>
+潢^</t>
+        </is>
+      </c>
+      <c r="C8" s="26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">가</t>
+        </is>
+      </c>
       <c r="D8" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢
-姑</t>
-        </is>
-      </c>
-      <c r="E8" s="32"/>
+          <t xml:space="preserve">㴌</t>
+        </is>
+      </c>
+      <c r="E8" s="26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">래</t>
+        </is>
+      </c>
       <c r="F8" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南
+△</t>
+        </is>
+      </c>
+      <c r="G8" s="26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">서</t>
+        </is>
+      </c>
+      <c r="H8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 △</t>
         </is>
       </c>
-      <c r="G8" s="32"/>
-      <c r="H8" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢</t>
-        </is>
-      </c>
-      <c r="I8" s="32"/>
-    </row>
-    <row r="9" ht="55.19" customHeight="1">
+      <c r="I8" s="26"/>
+      <c r="J8" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢^</t>
+        </is>
+      </c>
+      <c r="K8" s="26"/>
+    </row>
+    <row r="9" ht="59.7" customHeight="1">
       <c r="A9" s="0"/>
-      <c r="B9" s="24" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢潢
+      <c r="B9" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">㴌
 姑</t>
         </is>
       </c>
-      <c r="C9" s="33" t="inlineStr">
+      <c r="C9" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">못
+봤</t>
+        </is>
+      </c>
+      <c r="D9" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢^
+南</t>
+        </is>
+      </c>
+      <c r="E9" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">막
 혀</t>
         </is>
       </c>
-      <c r="D9" s="21" t="inlineStr">
+      <c r="F9" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢^
+姑</t>
+        </is>
+      </c>
+      <c r="G9" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">비
+치</t>
+        </is>
+      </c>
+      <c r="H9" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">㴌
+潢^</t>
+        </is>
+      </c>
+      <c r="I9" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">추
+월</t>
+        </is>
+      </c>
+      <c r="J9" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
-南</t>
-        </is>
-      </c>
-      <c r="E9" s="29" t="inlineStr">
-        <is>
-          <t xml:space="preserve">비</t>
-        </is>
-      </c>
-      <c r="F9" s="24" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢潢
-姑</t>
-        </is>
-      </c>
-      <c r="G9" s="33" t="inlineStr">
-        <is>
-          <t xml:space="preserve">추</t>
-        </is>
-      </c>
-      <c r="H9" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢汰
-潢汰</t>
-        </is>
-      </c>
-      <c r="I9" s="29"/>
-    </row>
-    <row r="10" ht="55.19" customHeight="1">
+㴌</t>
+        </is>
+      </c>
+      <c r="K9" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">나
+를</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="59.7" customHeight="1">
       <c r="A10" s="0"/>
       <c r="B10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="C10" s="30" t="inlineStr">
-        <is>
-          <t xml:space="preserve">막
-혀</t>
+      <c r="C10" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">앗</t>
         </is>
       </c>
       <c r="D10" s="21" t="inlineStr">
@@ -2730,152 +3298,221 @@
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="E10" s="30" t="inlineStr">
-        <is>
-          <t xml:space="preserve">치</t>
-        </is>
-      </c>
+      <c r="E10" s="25"/>
       <c r="F10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="G10" s="30"/>
+      <c r="G10" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">이</t>
+        </is>
+      </c>
       <c r="H10" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢汰</t>
-        </is>
-      </c>
-      <c r="I10" s="30"/>
-    </row>
-    <row r="11" ht="55.19" customHeight="1">
+          <t xml:space="preserve">㴌</t>
+        </is>
+      </c>
+      <c r="I10" s="25"/>
+      <c r="J10" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">㴌
+㴌</t>
+        </is>
+      </c>
+      <c r="K10" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">잃
+고</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="59.7" customHeight="1">
       <c r="A11" s="0"/>
       <c r="B11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="C11" s="32" t="inlineStr">
+      <c r="C11" s="26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">으</t>
+        </is>
+      </c>
+      <c r="D11" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="E11" s="26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">으</t>
+        </is>
+      </c>
+      <c r="F11" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南</t>
+        </is>
+      </c>
+      <c r="G11" s="26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">고</t>
+        </is>
+      </c>
+      <c r="H11" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–</t>
+        </is>
+      </c>
+      <c r="I11" s="26"/>
+      <c r="J11" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–
+ﾉ</t>
+        </is>
+      </c>
+      <c r="K11" s="28"/>
+    </row>
+    <row r="12" ht="59.7" customHeight="1">
+      <c r="A12" s="0"/>
+      <c r="B12" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南</t>
+        </is>
+      </c>
+      <c r="C12" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">니</t>
         </is>
       </c>
-      <c r="D11" s="24" t="inlineStr">
+      <c r="D12" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="E11" s="31"/>
-      <c r="F11" s="21" t="inlineStr">
+      <c r="E12" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">니</t>
+        </is>
+      </c>
+      <c r="F12" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="G11" s="32"/>
-      <c r="H11" s="24" t="inlineStr">
-        <is>
-          <t xml:space="preserve">／</t>
-        </is>
-      </c>
-      <c r="I11" s="31"/>
-    </row>
-    <row r="12" ht="55.19" customHeight="1">
-      <c r="A12" s="0"/>
-      <c r="B12" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">南</t>
-        </is>
-      </c>
-      <c r="C12" s="29" t="inlineStr">
-        <is>
-          <t xml:space="preserve">니</t>
-        </is>
-      </c>
-      <c r="D12" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="E12" s="29"/>
-      <c r="F12" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">南</t>
-        </is>
-      </c>
-      <c r="G12" s="29" t="inlineStr">
-        <is>
-          <t xml:space="preserve">갈</t>
-        </is>
-      </c>
-      <c r="H12" s="24" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢潢</t>
-        </is>
-      </c>
-      <c r="I12" s="33"/>
-    </row>
-    <row r="13" ht="55.19" customHeight="1">
+      <c r="G12" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">저</t>
+        </is>
+      </c>
+      <c r="H12" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–
+△</t>
+        </is>
+      </c>
+      <c r="I12" s="22"/>
+      <c r="J12" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢^
+潢^</t>
+        </is>
+      </c>
+      <c r="K12" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">어
+러</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="59.7" customHeight="1">
       <c r="A13" s="0"/>
       <c r="B13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="C13" s="30"/>
+      <c r="C13" s="25"/>
       <c r="D13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="E13" s="30"/>
+      <c r="E13" s="25"/>
       <c r="F13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="G13" s="30" t="inlineStr">
-        <is>
-          <t xml:space="preserve">이</t>
-        </is>
-      </c>
-      <c r="H13" s="24" t="inlineStr">
+      <c r="G13" s="25"/>
+      <c r="H13" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">㴌</t>
+        </is>
+      </c>
+      <c r="I13" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">같</t>
+        </is>
+      </c>
+      <c r="J13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="I13" s="34"/>
-    </row>
-    <row r="14" ht="55.19" customHeight="1">
+      <c r="K13" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">는</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="59.7" customHeight="1">
       <c r="A14" s="0"/>
       <c r="B14" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">–</t>
-        </is>
-      </c>
-      <c r="C14" s="32"/>
-      <c r="D14" s="21" t="inlineStr">
-        <is>
           <t xml:space="preserve">–
 △</t>
         </is>
       </c>
-      <c r="E14" s="32"/>
+      <c r="C14" s="26"/>
+      <c r="D14" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–
+△</t>
+        </is>
+      </c>
+      <c r="E14" s="26"/>
       <c r="F14" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">–</t>
-        </is>
-      </c>
-      <c r="G14" s="32"/>
-      <c r="H14" s="24" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢</t>
-        </is>
-      </c>
-      <c r="I14" s="31"/>
+          <t xml:space="preserve">△</t>
+        </is>
+      </c>
+      <c r="G14" s="26"/>
+      <c r="H14" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢^</t>
+        </is>
+      </c>
+      <c r="I14" s="26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">이</t>
+        </is>
+      </c>
+      <c r="J14" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢^</t>
+        </is>
+      </c>
+      <c r="K14" s="26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">가</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="B2:I2"/>
+    <mergeCell ref="B2:K2"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>

--- a/sheets/민요/검수/쑥대머리 (중모리).xlsx
+++ b/sheets/민요/검수/쑥대머리 (중모리).xlsx
@@ -601,10 +601,7 @@
       </patternFill>
     </fill>
     <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFF2CC"/>
-        <bgColor rgb="FFFFFFFF"/>
-      </patternFill>
+      <patternFill patternType="none"/>
     </fill>
   </fills>
   <borders count="5">

--- a/sheets/민요/검수/쑥대머리 (중모리).xlsx
+++ b/sheets/민요/검수/쑥대머리 (중모리).xlsx
@@ -547,17 +547,17 @@
     </font>
     <font>
       <sz val="10"/>
-      <name val="Arial"/>
+      <name val="궁서체"/>
       <family val="0"/>
     </font>
     <font>
       <sz val="10"/>
-      <name val="Arial"/>
+      <name val="궁서체"/>
       <family val="0"/>
     </font>
     <font>
       <sz val="10"/>
-      <name val="Arial"/>
+      <name val="궁서체"/>
       <family val="0"/>
     </font>
     <font>
@@ -674,7 +674,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="26">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -732,6 +732,50 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="7" fillId="3" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="3" borderId="2" xfId="0" applyFont="1" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="3" borderId="3" xfId="0" applyFont="1" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="3" borderId="4" xfId="0" applyFont="1" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -3024,380 +3068,380 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
+    <pageSetUpPr fitToPage="0"/>
   </sheetPr>
   <dimension ref="B1:K14"/>
   <sheetFormatPr defaultColWidth="8.5078125" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="2"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="15" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="16" width="6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="15" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="16" width="6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="15" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="16" width="6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="15" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="16" width="6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="15" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="16" width="6"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="2" customFormat="false" ht="59.7" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B2" s="6" t="s">
+    <row r="1" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="6.0" customHeight="true"/>
+    <row r="2" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="43.48" customHeight="true">
+      <c r="B2" s="17" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="6"/>
-      <c r="D2" s="6"/>
-      <c r="E2" s="6"/>
-      <c r="F2" s="6"/>
-      <c r="G2" s="6"/>
-      <c r="H2" s="6"/>
-      <c r="I2" s="6"/>
-      <c r="J2" s="6"/>
-      <c r="K2" s="6"/>
-    </row>
-    <row r="3" customFormat="false" ht="59.7" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B3" s="7" t="s">
+      <c r="C2" s="17"/>
+      <c r="D2" s="17"/>
+      <c r="E2" s="17"/>
+      <c r="F2" s="17"/>
+      <c r="G2" s="17"/>
+      <c r="H2" s="17"/>
+      <c r="I2" s="17"/>
+      <c r="J2" s="17"/>
+      <c r="K2" s="17"/>
+    </row>
+    <row r="3" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="64.57" customHeight="true">
+      <c r="B3" s="18" t="s">
         <v>91</v>
       </c>
-      <c r="C3" s="8" t="s">
+      <c r="C3" s="19" t="s">
         <v>120</v>
       </c>
-      <c r="D3" s="7" t="s">
+      <c r="D3" s="18" t="s">
         <v>110</v>
       </c>
-      <c r="E3" s="8" t="s">
+      <c r="E3" s="19" t="s">
         <v>135</v>
       </c>
-      <c r="F3" s="7" t="s">
+      <c r="F3" s="18" t="s">
         <v>91</v>
       </c>
-      <c r="G3" s="8" t="s">
+      <c r="G3" s="19" t="s">
         <v>92</v>
       </c>
-      <c r="H3" s="7" t="s">
+      <c r="H3" s="18" t="s">
         <v>72</v>
       </c>
-      <c r="I3" s="8" t="s">
+      <c r="I3" s="19" t="s">
         <v>73</v>
       </c>
-      <c r="J3" s="9" t="s">
+      <c r="J3" s="20" t="s">
         <v>47</v>
       </c>
-      <c r="K3" s="10" t="s">
+      <c r="K3" s="21" t="s">
         <v>136</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="59.7" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B4" s="7" t="s">
+    <row r="4" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="64.57" customHeight="true">
+      <c r="B4" s="18" t="s">
         <v>56</v>
       </c>
-      <c r="C4" s="11" t="s">
+      <c r="C4" s="22" t="s">
         <v>121</v>
       </c>
-      <c r="D4" s="7" t="s">
+      <c r="D4" s="18" t="s">
         <v>55</v>
       </c>
-      <c r="E4" s="11"/>
-      <c r="F4" s="7" t="s">
+      <c r="E4" s="22"/>
+      <c r="F4" s="18" t="s">
         <v>55</v>
       </c>
-      <c r="G4" s="11"/>
-      <c r="H4" s="7" t="s">
+      <c r="G4" s="22"/>
+      <c r="H4" s="18" t="s">
         <v>75</v>
       </c>
-      <c r="I4" s="11" t="s">
+      <c r="I4" s="22" t="s">
         <v>76</v>
       </c>
-      <c r="J4" s="7" t="s">
+      <c r="J4" s="18" t="s">
         <v>51</v>
       </c>
-      <c r="K4" s="11" t="s">
+      <c r="K4" s="22" t="s">
         <v>137</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="59.7" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B5" s="7" t="s">
+    <row r="5" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="64.57" customHeight="true">
+      <c r="B5" s="18" t="s">
         <v>138</v>
       </c>
-      <c r="C5" s="12" t="s">
+      <c r="C5" s="23" t="s">
         <v>139</v>
       </c>
-      <c r="D5" s="7" t="s">
+      <c r="D5" s="18" t="s">
         <v>55</v>
       </c>
-      <c r="E5" s="12"/>
-      <c r="F5" s="7" t="s">
+      <c r="E5" s="23"/>
+      <c r="F5" s="18" t="s">
         <v>94</v>
       </c>
-      <c r="G5" s="12" t="s">
+      <c r="G5" s="23" t="s">
         <v>140</v>
       </c>
-      <c r="H5" s="7" t="s">
+      <c r="H5" s="18" t="s">
         <v>78</v>
       </c>
-      <c r="I5" s="12" t="s">
+      <c r="I5" s="23" t="s">
         <v>141</v>
       </c>
-      <c r="J5" s="7" t="s">
+      <c r="J5" s="18" t="s">
         <v>51</v>
       </c>
-      <c r="K5" s="12" t="s">
+      <c r="K5" s="23" t="s">
         <v>142</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="59.7" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B6" s="9" t="s">
+    <row r="6" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="64.57" customHeight="true">
+      <c r="B6" s="20" t="s">
         <v>124</v>
       </c>
-      <c r="C6" s="10" t="s">
+      <c r="C6" s="21" t="s">
         <v>125</v>
       </c>
-      <c r="D6" s="7" t="s">
+      <c r="D6" s="18" t="s">
         <v>108</v>
       </c>
-      <c r="E6" s="8"/>
-      <c r="F6" s="7" t="s">
+      <c r="E6" s="19"/>
+      <c r="F6" s="18" t="s">
         <v>138</v>
       </c>
-      <c r="G6" s="8" t="s">
+      <c r="G6" s="19" t="s">
         <v>143</v>
       </c>
-      <c r="H6" s="7" t="s">
+      <c r="H6" s="18" t="s">
         <v>55</v>
       </c>
-      <c r="I6" s="8"/>
-      <c r="J6" s="7" t="s">
+      <c r="I6" s="19"/>
+      <c r="J6" s="18" t="s">
         <v>51</v>
       </c>
-      <c r="K6" s="8" t="s">
+      <c r="K6" s="19" t="s">
         <v>144</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="59.7" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B7" s="7" t="s">
+    <row r="7" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="64.57" customHeight="true">
+      <c r="B7" s="18" t="s">
         <v>91</v>
       </c>
-      <c r="C7" s="11" t="s">
+      <c r="C7" s="22" t="s">
         <v>127</v>
       </c>
-      <c r="D7" s="7" t="s">
+      <c r="D7" s="18" t="s">
         <v>112</v>
       </c>
-      <c r="E7" s="11" t="s">
+      <c r="E7" s="22" t="s">
         <v>113</v>
       </c>
-      <c r="F7" s="9" t="s">
+      <c r="F7" s="20" t="s">
         <v>97</v>
       </c>
-      <c r="G7" s="13" t="s">
+      <c r="G7" s="24" t="s">
         <v>98</v>
       </c>
-      <c r="H7" s="7" t="s">
+      <c r="H7" s="18" t="s">
         <v>55</v>
       </c>
-      <c r="I7" s="11"/>
-      <c r="J7" s="7" t="s">
+      <c r="I7" s="22"/>
+      <c r="J7" s="18" t="s">
         <v>55</v>
       </c>
-      <c r="K7" s="11"/>
-    </row>
-    <row r="8" customFormat="false" ht="59.7" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B8" s="7" t="s">
+      <c r="K7" s="22"/>
+    </row>
+    <row r="8" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="64.57" customHeight="true">
+      <c r="B8" s="18" t="s">
         <v>145</v>
       </c>
-      <c r="C8" s="12" t="s">
+      <c r="C8" s="23" t="s">
         <v>71</v>
       </c>
-      <c r="D8" s="7" t="s">
+      <c r="D8" s="18" t="s">
         <v>86</v>
       </c>
-      <c r="E8" s="12" t="s">
+      <c r="E8" s="23" t="s">
         <v>114</v>
       </c>
-      <c r="F8" s="7" t="s">
+      <c r="F8" s="18" t="s">
         <v>101</v>
       </c>
-      <c r="G8" s="12" t="s">
+      <c r="G8" s="23" t="s">
         <v>102</v>
       </c>
-      <c r="H8" s="7" t="s">
+      <c r="H8" s="18" t="s">
         <v>82</v>
       </c>
-      <c r="I8" s="12"/>
-      <c r="J8" s="7" t="s">
+      <c r="I8" s="23"/>
+      <c r="J8" s="18" t="s">
         <v>69</v>
       </c>
-      <c r="K8" s="12"/>
-    </row>
-    <row r="9" customFormat="false" ht="59.7" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B9" s="7" t="s">
+      <c r="K8" s="23"/>
+    </row>
+    <row r="9" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="64.57" customHeight="true">
+      <c r="B9" s="18" t="s">
         <v>131</v>
       </c>
-      <c r="C9" s="8" t="s">
+      <c r="C9" s="19" t="s">
         <v>146</v>
       </c>
-      <c r="D9" s="7" t="s">
+      <c r="D9" s="18" t="s">
         <v>147</v>
       </c>
-      <c r="E9" s="8" t="s">
+      <c r="E9" s="19" t="s">
         <v>148</v>
       </c>
-      <c r="F9" s="7" t="s">
+      <c r="F9" s="18" t="s">
         <v>149</v>
       </c>
-      <c r="G9" s="8" t="s">
+      <c r="G9" s="19" t="s">
         <v>150</v>
       </c>
-      <c r="H9" s="7" t="s">
+      <c r="H9" s="18" t="s">
         <v>138</v>
       </c>
-      <c r="I9" s="8" t="s">
+      <c r="I9" s="19" t="s">
         <v>151</v>
       </c>
-      <c r="J9" s="7" t="s">
+      <c r="J9" s="18" t="s">
         <v>58</v>
       </c>
-      <c r="K9" s="8" t="s">
+      <c r="K9" s="19" t="s">
         <v>152</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="59.7" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B10" s="7" t="s">
+    <row r="10" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="64.57" customHeight="true">
+      <c r="B10" s="18" t="s">
         <v>72</v>
       </c>
-      <c r="C10" s="11" t="s">
+      <c r="C10" s="22" t="s">
         <v>133</v>
       </c>
-      <c r="D10" s="7" t="s">
+      <c r="D10" s="18" t="s">
         <v>55</v>
       </c>
-      <c r="E10" s="11"/>
-      <c r="F10" s="7" t="s">
+      <c r="E10" s="22"/>
+      <c r="F10" s="18" t="s">
         <v>72</v>
       </c>
-      <c r="G10" s="11" t="s">
+      <c r="G10" s="22" t="s">
         <v>90</v>
       </c>
-      <c r="H10" s="7" t="s">
+      <c r="H10" s="18" t="s">
         <v>86</v>
       </c>
-      <c r="I10" s="11"/>
-      <c r="J10" s="7" t="s">
+      <c r="I10" s="22"/>
+      <c r="J10" s="18" t="s">
         <v>61</v>
       </c>
-      <c r="K10" s="11" t="s">
+      <c r="K10" s="22" t="s">
         <v>153</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="59.7" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B11" s="7" t="s">
+    <row r="11" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="64.57" customHeight="true">
+      <c r="B11" s="18" t="s">
         <v>91</v>
       </c>
-      <c r="C11" s="12" t="s">
+      <c r="C11" s="23" t="s">
         <v>118</v>
       </c>
-      <c r="D11" s="7" t="s">
+      <c r="D11" s="18" t="s">
         <v>72</v>
       </c>
-      <c r="E11" s="12" t="s">
+      <c r="E11" s="23" t="s">
         <v>118</v>
       </c>
-      <c r="F11" s="7" t="s">
+      <c r="F11" s="18" t="s">
         <v>91</v>
       </c>
-      <c r="G11" s="12" t="s">
+      <c r="G11" s="23" t="s">
         <v>106</v>
       </c>
-      <c r="H11" s="7" t="s">
+      <c r="H11" s="18" t="s">
         <v>55</v>
       </c>
-      <c r="I11" s="12"/>
-      <c r="J11" s="9" t="s">
+      <c r="I11" s="23"/>
+      <c r="J11" s="20" t="s">
         <v>64</v>
       </c>
-      <c r="K11" s="14"/>
-    </row>
-    <row r="12" customFormat="false" ht="59.7" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B12" s="9" t="s">
+      <c r="K11" s="25"/>
+    </row>
+    <row r="12" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="64.57" customHeight="true">
+      <c r="B12" s="20" t="s">
         <v>91</v>
       </c>
-      <c r="C12" s="10" t="s">
+      <c r="C12" s="21" t="s">
         <v>119</v>
       </c>
-      <c r="D12" s="7" t="s">
+      <c r="D12" s="18" t="s">
         <v>72</v>
       </c>
-      <c r="E12" s="8" t="s">
+      <c r="E12" s="19" t="s">
         <v>119</v>
       </c>
-      <c r="F12" s="7" t="s">
+      <c r="F12" s="18" t="s">
         <v>91</v>
       </c>
-      <c r="G12" s="8" t="s">
+      <c r="G12" s="19" t="s">
         <v>107</v>
       </c>
-      <c r="H12" s="7" t="s">
+      <c r="H12" s="18" t="s">
         <v>82</v>
       </c>
-      <c r="I12" s="8"/>
-      <c r="J12" s="7" t="s">
+      <c r="I12" s="19"/>
+      <c r="J12" s="18" t="s">
         <v>51</v>
       </c>
-      <c r="K12" s="8" t="s">
+      <c r="K12" s="19" t="s">
         <v>154</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="59.7" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B13" s="7" t="s">
+    <row r="13" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="64.57" customHeight="true">
+      <c r="B13" s="18" t="s">
         <v>55</v>
       </c>
-      <c r="C13" s="11"/>
-      <c r="D13" s="7" t="s">
+      <c r="C13" s="22"/>
+      <c r="D13" s="18" t="s">
         <v>55</v>
       </c>
-      <c r="E13" s="11"/>
-      <c r="F13" s="7" t="s">
+      <c r="E13" s="22"/>
+      <c r="F13" s="18" t="s">
         <v>55</v>
       </c>
-      <c r="G13" s="11"/>
-      <c r="H13" s="7" t="s">
+      <c r="G13" s="22"/>
+      <c r="H13" s="18" t="s">
         <v>86</v>
       </c>
-      <c r="I13" s="11" t="s">
+      <c r="I13" s="22" t="s">
         <v>89</v>
       </c>
-      <c r="J13" s="7" t="s">
+      <c r="J13" s="18" t="s">
         <v>69</v>
       </c>
-      <c r="K13" s="11" t="s">
+      <c r="K13" s="22" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="59.7" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B14" s="7" t="s">
+    <row r="14" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="64.57" customHeight="true">
+      <c r="B14" s="18" t="s">
         <v>82</v>
       </c>
-      <c r="C14" s="12"/>
-      <c r="D14" s="7" t="s">
+      <c r="C14" s="23"/>
+      <c r="D14" s="18" t="s">
         <v>82</v>
       </c>
-      <c r="E14" s="12"/>
-      <c r="F14" s="7" t="s">
+      <c r="E14" s="23"/>
+      <c r="F14" s="18" t="s">
         <v>108</v>
       </c>
-      <c r="G14" s="12"/>
-      <c r="H14" s="7" t="s">
+      <c r="G14" s="23"/>
+      <c r="H14" s="18" t="s">
         <v>69</v>
       </c>
-      <c r="I14" s="12" t="s">
+      <c r="I14" s="23" t="s">
         <v>90</v>
       </c>
-      <c r="J14" s="7" t="s">
+      <c r="J14" s="18" t="s">
         <v>69</v>
       </c>
-      <c r="K14" s="12" t="s">
+      <c r="K14" s="23" t="s">
         <v>71</v>
       </c>
     </row>
@@ -3407,7 +3451,7 @@
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="true" verticalCentered="false"/>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageSetup paperSize="9" orientation="portrait" scale="92"/>
   <headerFooter differentFirst="false" differentOddEven="false">
     <oddHeader/>
     <oddFooter/>

--- a/sheets/민요/검수/쑥대머리 (중모리).xlsx
+++ b/sheets/민요/검수/쑥대머리 (중모리).xlsx
@@ -3074,20 +3074,20 @@
   <sheetFormatPr defaultColWidth="8.5078125" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="2"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="15" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="15" width="10.71"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="16" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="15" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="15" width="10.71"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="16" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="15" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="15" width="10.71"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="16" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="15" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="15" width="10.71"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="16" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="15" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="15" width="10.71"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="16" width="6"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="6.0" customHeight="true"/>
-    <row r="2" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="43.48" customHeight="true">
+    <row r="2" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="43.01" customHeight="true">
       <c r="B2" s="17" t="s">
         <v>0</v>
       </c>
@@ -3101,7 +3101,7 @@
       <c r="J2" s="17"/>
       <c r="K2" s="17"/>
     </row>
-    <row r="3" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="64.57" customHeight="true">
+    <row r="3" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="63.87" customHeight="true">
       <c r="B3" s="18" t="s">
         <v>91</v>
       </c>
@@ -3133,7 +3133,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="4" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="64.57" customHeight="true">
+    <row r="4" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="63.87" customHeight="true">
       <c r="B4" s="18" t="s">
         <v>56</v>
       </c>
@@ -3161,7 +3161,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="5" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="64.57" customHeight="true">
+    <row r="5" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="63.87" customHeight="true">
       <c r="B5" s="18" t="s">
         <v>138</v>
       </c>
@@ -3191,7 +3191,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="6" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="64.57" customHeight="true">
+    <row r="6" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="63.87" customHeight="true">
       <c r="B6" s="20" t="s">
         <v>124</v>
       </c>
@@ -3219,7 +3219,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="7" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="64.57" customHeight="true">
+    <row r="7" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="63.87" customHeight="true">
       <c r="B7" s="18" t="s">
         <v>91</v>
       </c>
@@ -3247,7 +3247,7 @@
       </c>
       <c r="K7" s="22"/>
     </row>
-    <row r="8" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="64.57" customHeight="true">
+    <row r="8" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="63.87" customHeight="true">
       <c r="B8" s="18" t="s">
         <v>145</v>
       </c>
@@ -3275,7 +3275,7 @@
       </c>
       <c r="K8" s="23"/>
     </row>
-    <row r="9" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="64.57" customHeight="true">
+    <row r="9" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="63.87" customHeight="true">
       <c r="B9" s="18" t="s">
         <v>131</v>
       </c>
@@ -3307,7 +3307,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="10" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="64.57" customHeight="true">
+    <row r="10" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="63.87" customHeight="true">
       <c r="B10" s="18" t="s">
         <v>72</v>
       </c>
@@ -3335,7 +3335,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="11" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="64.57" customHeight="true">
+    <row r="11" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="63.87" customHeight="true">
       <c r="B11" s="18" t="s">
         <v>91</v>
       </c>
@@ -3363,7 +3363,7 @@
       </c>
       <c r="K11" s="25"/>
     </row>
-    <row r="12" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="64.57" customHeight="true">
+    <row r="12" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="63.87" customHeight="true">
       <c r="B12" s="20" t="s">
         <v>91</v>
       </c>
@@ -3393,7 +3393,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="13" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="64.57" customHeight="true">
+    <row r="13" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="63.87" customHeight="true">
       <c r="B13" s="18" t="s">
         <v>55</v>
       </c>
@@ -3419,7 +3419,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="14" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="64.57" customHeight="true">
+    <row r="14" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="63.87" customHeight="true">
       <c r="B14" s="18" t="s">
         <v>82</v>
       </c>
@@ -3451,7 +3451,7 @@
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="true" verticalCentered="false"/>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" orientation="portrait" scale="92"/>
+  <pageSetup paperSize="9" orientation="portrait" scale="93"/>
   <headerFooter differentFirst="false" differentOddEven="false">
     <oddHeader/>
     <oddFooter/>
